--- a/inputData/LTM_demand.xlsx
+++ b/inputData/LTM_demand.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,16 +465,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>476</v>
+        <v>436</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -485,16 +485,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -508,16 +508,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>485</v>
+        <v>464</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -545,19 +545,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -571,10 +571,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -585,16 +585,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -605,19 +605,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -625,16 +625,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -645,19 +645,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -668,13 +668,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -685,13 +685,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -711,7 +711,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
@@ -725,19 +725,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -745,16 +745,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -765,19 +765,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -785,19 +785,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -805,16 +805,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -825,19 +825,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -845,19 +845,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -865,16 +865,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -885,16 +885,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
@@ -931,13 +931,13 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -948,10 +948,10 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
@@ -965,19 +965,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -985,16 +985,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>535</v>
+        <v>556</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1005,19 +1005,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>536</v>
+        <v>559</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1025,16 +1025,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>538</v>
+        <v>561</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1048,13 +1048,13 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1065,19 +1065,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
         <v>5</v>
       </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
       <c r="D32" t="n">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1088,16 +1088,16 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1108,10 +1108,10 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="E34" t="n">
         <v>2</v>
@@ -1125,16 +1125,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -1145,16 +1145,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1168,16 +1168,16 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>549</v>
+        <v>573</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1185,19 +1185,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>550</v>
+        <v>573</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1205,16 +1205,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1231,10 +1231,10 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>553</v>
+        <v>577</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1248,13 +1248,13 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>554</v>
+        <v>583</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1268,16 +1268,16 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>557</v>
+        <v>584</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1288,16 +1288,16 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1305,13 +1305,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
@@ -1325,19 +1325,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1348,16 +1348,16 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1365,13 +1365,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>572</v>
+        <v>602</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -1385,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>574</v>
+        <v>604</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -1405,13 +1405,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="E49" t="n">
         <v>3</v>
@@ -1425,19 +1425,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>581</v>
+        <v>630</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1445,19 +1445,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>581</v>
+        <v>633</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1465,16 +1465,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>583</v>
+        <v>659</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -1488,13 +1488,13 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>584</v>
+        <v>683</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -1505,16 +1505,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>589</v>
+        <v>777</v>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -1525,19 +1525,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>594</v>
+        <v>778</v>
       </c>
       <c r="E55" t="n">
         <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1545,16 +1545,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>602</v>
+        <v>832</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -1565,19 +1565,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>605</v>
+        <v>835</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1585,16 +1585,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>637</v>
+        <v>852</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -1605,16 +1605,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>682</v>
+        <v>855</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -1625,19 +1625,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>700</v>
+        <v>862</v>
       </c>
       <c r="E60" t="n">
         <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1645,16 +1645,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -1665,19 +1665,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="E62" t="n">
         <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1688,10 +1688,10 @@
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>856</v>
+        <v>867</v>
       </c>
       <c r="E63" t="n">
         <v>4</v>
@@ -1708,16 +1708,16 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1725,19 +1725,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="E65" t="n">
         <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1745,16 +1745,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
@@ -1765,19 +1765,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1785,19 +1785,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>905</v>
+        <v>885</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -1805,16 +1805,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>907</v>
+        <v>890</v>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -1825,16 +1825,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>910</v>
+        <v>891</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
@@ -1845,13 +1845,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>914</v>
+        <v>895</v>
       </c>
       <c r="E71" t="n">
         <v>4</v>
@@ -1865,16 +1865,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>918</v>
+        <v>902</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
@@ -1885,16 +1885,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
@@ -1905,13 +1905,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="E74" t="n">
         <v>4</v>
@@ -1928,10 +1928,10 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="E75" t="n">
         <v>4</v>
@@ -1945,19 +1945,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>945</v>
+        <v>931</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -1965,19 +1965,19 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>946</v>
+        <v>933</v>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -1985,19 +1985,19 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2005,19 +2005,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="E79" t="n">
         <v>4</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2025,16 +2025,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>962</v>
+        <v>950</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
@@ -2045,16 +2045,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>964</v>
+        <v>952</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -2068,16 +2068,16 @@
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>972</v>
+        <v>955</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2085,19 +2085,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D83" t="n">
-        <v>974</v>
+        <v>960</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2105,16 +2105,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D84" t="n">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2125,19 +2125,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>975</v>
+        <v>984</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -2145,19 +2145,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="E86" t="n">
         <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2165,19 +2165,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2185,16 +2185,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -2205,16 +2205,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -2225,19 +2225,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2245,16 +2245,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -2265,16 +2265,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -2285,16 +2285,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C93" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -2308,13 +2308,13 @@
         <v>4</v>
       </c>
       <c r="C94" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>1028</v>
+        <v>1056</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -2325,16 +2325,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1037</v>
+        <v>1060</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
@@ -2345,16 +2345,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C96" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1039</v>
+        <v>1060</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
@@ -2365,13 +2365,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>1042</v>
+        <v>1063</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
@@ -2385,16 +2385,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>1061</v>
+        <v>1071</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -2405,19 +2405,19 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2425,16 +2425,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -2445,13 +2445,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="E101" t="n">
         <v>3</v>
@@ -2468,13 +2468,13 @@
         <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="E102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
@@ -2485,16 +2485,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>1104</v>
+        <v>1122</v>
       </c>
       <c r="E103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -2505,13 +2505,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="E104" t="n">
         <v>1</v>
@@ -2525,19 +2525,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C105" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>1114</v>
+        <v>1128</v>
       </c>
       <c r="E105" t="n">
         <v>4</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2545,16 +2545,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -2565,19 +2565,19 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C107" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>1133</v>
+        <v>1164</v>
       </c>
       <c r="E107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -2585,118 +2585,18 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>1144</v>
+        <v>1184</v>
       </c>
       <c r="E108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" t="n">
-        <v>7</v>
-      </c>
-      <c r="C109" t="n">
-        <v>1</v>
-      </c>
-      <c r="D109" t="n">
-        <v>1145</v>
-      </c>
-      <c r="E109" t="n">
-        <v>3</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" t="n">
-        <v>1</v>
-      </c>
-      <c r="C110" t="n">
-        <v>6</v>
-      </c>
-      <c r="D110" t="n">
-        <v>1168</v>
-      </c>
-      <c r="E110" t="n">
-        <v>3</v>
-      </c>
-      <c r="F110" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" t="n">
-        <v>4</v>
-      </c>
-      <c r="C111" t="n">
-        <v>8</v>
-      </c>
-      <c r="D111" t="n">
-        <v>1170</v>
-      </c>
-      <c r="E111" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" t="n">
-        <v>2</v>
-      </c>
-      <c r="C112" t="n">
-        <v>1</v>
-      </c>
-      <c r="D112" t="n">
-        <v>1172</v>
-      </c>
-      <c r="E112" t="n">
-        <v>3</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" t="n">
-        <v>4</v>
-      </c>
-      <c r="C113" t="n">
-        <v>8</v>
-      </c>
-      <c r="D113" t="n">
-        <v>1183</v>
-      </c>
-      <c r="E113" t="n">
-        <v>4</v>
-      </c>
-      <c r="F113" t="n">
         <v>0</v>
       </c>
     </row>

--- a/inputData/LTM_demand.xlsx
+++ b/inputData/LTM_demand.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,16 +465,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>436</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -488,13 +488,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>452</v>
+        <v>37</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -505,19 +505,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>464</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -525,16 +525,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>481</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -545,19 +545,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>492</v>
+        <v>69</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -565,13 +565,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>498</v>
+        <v>71</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -585,13 +585,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>506</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -605,19 +605,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>508</v>
+        <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -631,10 +631,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>511</v>
+        <v>81</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -645,19 +645,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>514</v>
+        <v>81</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -668,16 +668,16 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>517</v>
+        <v>83</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -688,16 +688,16 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>518</v>
+        <v>86</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -711,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>520</v>
+        <v>88</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -725,16 +725,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>521</v>
+        <v>89</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -745,16 +745,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>524</v>
+        <v>94</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -765,16 +765,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>524</v>
+        <v>95</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -785,19 +785,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>526</v>
+        <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -805,16 +805,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>526</v>
+        <v>99</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -828,16 +828,16 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>530</v>
+        <v>99</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -845,16 +845,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>533</v>
+        <v>102</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -865,19 +865,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>534</v>
+        <v>104</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -885,19 +885,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>534</v>
+        <v>108</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -905,19 +905,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>535</v>
+        <v>110</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -925,19 +925,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>546</v>
+        <v>114</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -945,13 +945,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>547</v>
+        <v>119</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
@@ -965,19 +965,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>551</v>
+        <v>119</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -985,19 +985,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>556</v>
+        <v>121</v>
       </c>
       <c r="E28" t="n">
         <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1008,10 +1008,10 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>559</v>
+        <v>122</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -1028,16 +1028,16 @@
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>561</v>
+        <v>127</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1045,19 +1045,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>564</v>
+        <v>133</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1068,13 +1068,13 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>564</v>
+        <v>133</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -1085,19 +1085,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>570</v>
+        <v>133</v>
       </c>
       <c r="E33" t="n">
         <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1105,16 +1105,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>570</v>
+        <v>137</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>571</v>
+        <v>140</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1145,19 +1145,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>571</v>
+        <v>142</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1171,7 +1171,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>573</v>
+        <v>144</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>573</v>
+        <v>146</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -1205,16 +1205,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>577</v>
+        <v>148</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1231,13 +1231,13 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>577</v>
+        <v>150</v>
       </c>
       <c r="E40" t="n">
         <v>4</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1245,19 +1245,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>583</v>
+        <v>158</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1268,13 +1268,13 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>584</v>
+        <v>160</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1285,16 +1285,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>584</v>
+        <v>160</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -1311,13 +1311,13 @@
         <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>592</v>
+        <v>164</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1325,13 +1325,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>592</v>
+        <v>166</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
@@ -1348,13 +1348,13 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>599</v>
+        <v>190</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -1365,13 +1365,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>602</v>
+        <v>193</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -1385,19 +1385,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>604</v>
+        <v>205</v>
       </c>
       <c r="E48" t="n">
         <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1405,19 +1405,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>608</v>
+        <v>216</v>
       </c>
       <c r="E49" t="n">
         <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1425,19 +1425,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>630</v>
+        <v>222</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1445,19 +1445,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>633</v>
+        <v>229</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1471,13 +1471,13 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>659</v>
+        <v>260</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1491,13 +1491,13 @@
         <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>683</v>
+        <v>314</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1505,19 +1505,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>777</v>
+        <v>370</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1525,16 +1525,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>778</v>
+        <v>426</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1545,19 +1545,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>832</v>
+        <v>444</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1571,13 +1571,13 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>835</v>
+        <v>444</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1591,10 +1591,10 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>852</v>
+        <v>446</v>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -1605,19 +1605,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>855</v>
+        <v>449</v>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1631,10 +1631,10 @@
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>862</v>
+        <v>452</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -1645,19 +1645,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>863</v>
+        <v>455</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1671,10 +1671,10 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>863</v>
+        <v>459</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -1691,13 +1691,13 @@
         <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>867</v>
+        <v>471</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1711,13 +1711,13 @@
         <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>868</v>
+        <v>483</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -1725,16 +1725,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>873</v>
+        <v>491</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -1748,16 +1748,16 @@
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>875</v>
+        <v>493</v>
       </c>
       <c r="E66" t="n">
         <v>3</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1765,16 +1765,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>882</v>
+        <v>499</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -1785,19 +1785,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>885</v>
+        <v>503</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1808,13 +1808,13 @@
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>890</v>
+        <v>509</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -1825,16 +1825,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>891</v>
+        <v>512</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
@@ -1851,13 +1851,13 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>895</v>
+        <v>516</v>
       </c>
       <c r="E71" t="n">
         <v>4</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1865,19 +1865,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>902</v>
+        <v>523</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1885,19 +1885,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>912</v>
+        <v>533</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1905,13 +1905,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>913</v>
+        <v>536</v>
       </c>
       <c r="E74" t="n">
         <v>4</v>
@@ -1928,13 +1928,13 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>924</v>
+        <v>538</v>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
@@ -1945,19 +1945,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>931</v>
+        <v>540</v>
       </c>
       <c r="E76" t="n">
         <v>3</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1965,13 +1965,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>933</v>
+        <v>540</v>
       </c>
       <c r="E77" t="n">
         <v>2</v>
@@ -1991,10 +1991,10 @@
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>941</v>
+        <v>544</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -2005,19 +2005,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>948</v>
+        <v>547</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2025,19 +2025,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>950</v>
+        <v>550</v>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2051,7 +2051,7 @@
         <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>952</v>
+        <v>550</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -2065,16 +2065,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>955</v>
+        <v>553</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -2085,19 +2085,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>960</v>
+        <v>554</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2105,19 +2105,19 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>969</v>
+        <v>564</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2125,19 +2125,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>984</v>
+        <v>570</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2145,16 +2145,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>992</v>
+        <v>576</v>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2171,10 +2171,10 @@
         <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>998</v>
+        <v>577</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -2185,19 +2185,19 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>1000</v>
+        <v>582</v>
       </c>
       <c r="E88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2211,13 +2211,13 @@
         <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>1001</v>
+        <v>588</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2225,19 +2225,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>1002</v>
+        <v>596</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -2251,10 +2251,10 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1007</v>
+        <v>596</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -2268,13 +2268,13 @@
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>1015</v>
+        <v>605</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -2285,19 +2285,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1032</v>
+        <v>613</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2311,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>1056</v>
+        <v>616</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -2331,13 +2331,13 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1060</v>
+        <v>618</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2345,13 +2345,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>1060</v>
+        <v>621</v>
       </c>
       <c r="E96" t="n">
         <v>3</v>
@@ -2365,19 +2365,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>1063</v>
+        <v>622</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -2385,16 +2385,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>1071</v>
+        <v>628</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -2405,16 +2405,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>1080</v>
+        <v>635</v>
       </c>
       <c r="E99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>1081</v>
+        <v>649</v>
       </c>
       <c r="E100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2445,19 +2445,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>1087</v>
+        <v>654</v>
       </c>
       <c r="E101" t="n">
         <v>3</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -2465,19 +2465,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>1095</v>
+        <v>667</v>
       </c>
       <c r="E102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2488,13 +2488,13 @@
         <v>1</v>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>1122</v>
+        <v>668</v>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -2505,16 +2505,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>1125</v>
+        <v>688</v>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
@@ -2525,16 +2525,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>1128</v>
+        <v>712</v>
       </c>
       <c r="E105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
@@ -2545,13 +2545,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>1129</v>
+        <v>720</v>
       </c>
       <c r="E106" t="n">
         <v>2</v>
@@ -2565,38 +2565,18 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>1164</v>
+        <v>741</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" t="n">
-        <v>2</v>
-      </c>
-      <c r="C108" t="n">
-        <v>1</v>
-      </c>
-      <c r="D108" t="n">
-        <v>1184</v>
-      </c>
-      <c r="E108" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" t="n">
         <v>0</v>
       </c>
     </row>

--- a/inputData/LTM_demand.xlsx
+++ b/inputData/LTM_demand.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3326953A-7A21-4AFF-A34D-8F5984C0D1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2E1A76-1D7B-4062-88EF-7093FC39BE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PassengerGroups" sheetId="1" r:id="rId1"/>
@@ -444,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -725,286 +725,6 @@
       </c>
       <c r="F14">
         <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>4</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>411</v>
-      </c>
-      <c r="E15">
-        <v>4</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>5</v>
-      </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16">
-        <v>422</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17">
-        <v>454</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
-      <c r="D18">
-        <v>454</v>
-      </c>
-      <c r="E18">
-        <v>4</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>529</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>4</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>560</v>
-      </c>
-      <c r="E20">
-        <v>3</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>562</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>5</v>
-      </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22">
-        <v>578</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>2</v>
-      </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23">
-        <v>582</v>
-      </c>
-      <c r="E23">
-        <v>4</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>4</v>
-      </c>
-      <c r="D24">
-        <v>652</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>2</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>654</v>
-      </c>
-      <c r="E25">
-        <v>4</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26">
-        <v>4</v>
-      </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>659</v>
-      </c>
-      <c r="E26">
-        <v>4</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>4</v>
-      </c>
-      <c r="D27">
-        <v>663</v>
-      </c>
-      <c r="E27">
-        <v>3</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>4</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>747</v>
-      </c>
-      <c r="E28">
-        <v>4</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/inputData/LTM_demand.xlsx
+++ b/inputData/LTM_demand.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,13 +465,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -485,16 +485,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -505,19 +505,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -525,13 +525,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -568,13 +568,13 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -585,16 +585,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -605,13 +605,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -625,19 +625,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -651,10 +651,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -665,16 +665,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -685,16 +685,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>192</v>
+        <v>109</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -725,16 +725,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>199</v>
+        <v>113</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -745,13 +745,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>199</v>
+        <v>132</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -765,16 +765,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>384</v>
+        <v>149</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -785,19 +785,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>468</v>
+        <v>150</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -805,16 +805,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>504</v>
+        <v>150</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -825,19 +825,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>515</v>
+        <v>152</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -845,19 +845,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>515</v>
+        <v>163</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -865,19 +865,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>527</v>
+        <v>165</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -885,19 +885,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>541</v>
+        <v>170</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -905,19 +905,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>553</v>
+        <v>190</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -925,16 +925,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>555</v>
+        <v>286</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -945,16 +945,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>587</v>
+        <v>329</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -965,16 +965,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>618</v>
+        <v>379</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -985,16 +985,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>660</v>
+        <v>399</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -1005,19 +1005,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>690</v>
+        <v>411</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1025,16 +1025,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>705</v>
+        <v>416</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -1048,13 +1048,13 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>721</v>
+        <v>421</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -1068,16 +1068,616 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>738</v>
+        <v>444</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>479</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>489</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>516</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>520</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>536</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="n">
+        <v>10</v>
+      </c>
+      <c r="D38" t="n">
+        <v>549</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>552</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" t="n">
+        <v>553</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>560</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="n">
+        <v>577</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>579</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>7</v>
+      </c>
+      <c r="D44" t="n">
+        <v>581</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="n">
+        <v>604</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>608</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>608</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>611</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" t="n">
+        <v>630</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D50" t="n">
+        <v>633</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>7</v>
+      </c>
+      <c r="D51" t="n">
+        <v>639</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" t="n">
+        <v>7</v>
+      </c>
+      <c r="D52" t="n">
+        <v>644</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>9</v>
+      </c>
+      <c r="D53" t="n">
+        <v>647</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>9</v>
+      </c>
+      <c r="D54" t="n">
+        <v>649</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>10</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>651</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+      <c r="D56" t="n">
+        <v>664</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="n">
+        <v>676</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>696</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>708</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>7</v>
+      </c>
+      <c r="D60" t="n">
+        <v>709</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>6</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>742</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>10</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="n">
+        <v>776</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/inputData/LTM_demand.xlsx
+++ b/inputData/LTM_demand.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,19 +465,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -485,19 +485,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -505,16 +505,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -525,19 +525,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -548,16 +548,16 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -571,13 +571,13 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -591,10 +591,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -625,19 +625,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -645,19 +645,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -671,13 +671,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -685,19 +685,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -705,13 +705,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -725,19 +725,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -748,13 +748,13 @@
         <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -765,16 +765,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -785,16 +785,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -825,16 +825,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -845,16 +845,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -865,19 +865,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>165</v>
+        <v>210</v>
       </c>
       <c r="E22" t="n">
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -885,16 +885,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>170</v>
+        <v>227</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -905,19 +905,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>190</v>
+        <v>263</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -925,13 +925,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>286</v>
+        <v>376</v>
       </c>
       <c r="E25" t="n">
         <v>4</v>
@@ -945,19 +945,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>329</v>
+        <v>378</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -965,19 +965,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -988,16 +988,16 @@
         <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1005,19 +1005,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1025,19 +1025,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>416</v>
+        <v>450</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1045,13 +1045,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
@@ -1068,10 +1068,10 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="E32" t="n">
         <v>4</v>
@@ -1085,13 +1085,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
@@ -1111,10 +1111,10 @@
         <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -1125,13 +1125,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>516</v>
+        <v>474</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
@@ -1148,16 +1148,16 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>520</v>
+        <v>476</v>
       </c>
       <c r="E36" t="n">
         <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1165,19 +1165,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>536</v>
+        <v>487</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1185,16 +1185,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>549</v>
+        <v>491</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
@@ -1205,19 +1205,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>552</v>
+        <v>507</v>
       </c>
       <c r="E39" t="n">
         <v>4</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1225,13 +1225,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
@@ -1245,13 +1245,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>560</v>
+        <v>526</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
@@ -1265,16 +1265,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>577</v>
+        <v>528</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -1285,13 +1285,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
         <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>579</v>
+        <v>543</v>
       </c>
       <c r="E43" t="n">
         <v>3</v>
@@ -1305,19 +1305,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>581</v>
+        <v>545</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1325,13 +1325,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>604</v>
+        <v>550</v>
       </c>
       <c r="E45" t="n">
         <v>4</v>
@@ -1345,13 +1345,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>608</v>
+        <v>556</v>
       </c>
       <c r="E46" t="n">
         <v>4</v>
@@ -1365,16 +1365,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>608</v>
+        <v>563</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>611</v>
+        <v>570</v>
       </c>
       <c r="E48" t="n">
         <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1405,16 +1405,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>630</v>
+        <v>571</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -1425,19 +1425,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>633</v>
+        <v>579</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1448,16 +1448,16 @@
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>639</v>
+        <v>590</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1465,13 +1465,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>644</v>
+        <v>604</v>
       </c>
       <c r="E52" t="n">
         <v>4</v>
@@ -1485,13 +1485,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>647</v>
+        <v>610</v>
       </c>
       <c r="E53" t="n">
         <v>4</v>
@@ -1508,16 +1508,16 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>649</v>
+        <v>613</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1525,16 +1525,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>651</v>
+        <v>615</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1545,16 +1545,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>664</v>
+        <v>636</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -1565,13 +1565,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
-        <v>676</v>
+        <v>648</v>
       </c>
       <c r="E57" t="n">
         <v>4</v>
@@ -1585,19 +1585,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>696</v>
+        <v>675</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1611,7 +1611,7 @@
         <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>708</v>
+        <v>676</v>
       </c>
       <c r="E59" t="n">
         <v>4</v>
@@ -1628,16 +1628,16 @@
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1645,19 +1645,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
         <v>6</v>
       </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
       <c r="D61" t="n">
-        <v>742</v>
+        <v>700</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1665,19 +1665,39 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>776</v>
+        <v>703</v>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" t="n">
+        <v>707</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
